--- a/list.xlsx
+++ b/list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saikishi-my.sharepoint.com/personal/t0011_saikishi_onmicrosoft_com/Documents/OneDriveドキュメント/100ex www(outer)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{4C74CA03-677A-4304-846F-ED1ADA66BAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EECAB90-9453-4656-A2FD-20C23249DED2}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{4C74CA03-677A-4304-846F-ED1ADA66BAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B61F1A69-60F7-456C-8D09-99822A59F9F1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="1740" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="112">
   <si>
     <t>title</t>
   </si>
@@ -699,13 +699,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>技術</t>
-    <rPh sb="0" eb="2">
-      <t>ギジュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>りずむクエスト</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -731,6 +724,34 @@
     <rPh sb="3" eb="7">
       <t>ガッキュウカツドウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>じゃんけんゲームをつくろう</t>
+  </si>
+  <si>
+    <t>3nenJanken</t>
+  </si>
+  <si>
+    <t>小３算数の教科書より。</t>
+  </si>
+  <si>
+    <t>◯</t>
+  </si>
+  <si>
+    <t>プログラミング</t>
+  </si>
+  <si>
+    <t>４年算数プログラミングコーナー</t>
+  </si>
+  <si>
+    <t>4nenpgm</t>
+  </si>
+  <si>
+    <t>小４算数の教科書より。すごろくと、がい数計算機のしくみを探ろう</t>
+  </si>
+  <si>
+    <t>プログラミング</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1056,15 +1077,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:O29"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="12.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="71.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="71.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1148,7 +1169,7 @@
         <v>59</v>
       </c>
       <c r="O3" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1794,36 +1815,70 @@
         <v>78</v>
       </c>
       <c r="O26" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
         <v>100</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>101</v>
       </c>
-      <c r="D27" t="s">
+      <c r="I27" t="s">
+        <v>78</v>
+      </c>
+      <c r="J27" t="s">
+        <v>78</v>
+      </c>
+      <c r="K27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L27" t="s">
+        <v>78</v>
+      </c>
+      <c r="M27" t="s">
+        <v>78</v>
+      </c>
+      <c r="O27" t="s">
         <v>102</v>
       </c>
-      <c r="I27" t="s">
-        <v>78</v>
-      </c>
-      <c r="J27" t="s">
-        <v>78</v>
-      </c>
-      <c r="K27" t="s">
-        <v>78</v>
-      </c>
-      <c r="L27" t="s">
-        <v>78</v>
-      </c>
-      <c r="M27" t="s">
-        <v>78</v>
-      </c>
-      <c r="O27" t="s">
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
         <v>103</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" t="s">
+        <v>106</v>
+      </c>
+      <c r="O28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H29" t="s">
+        <v>106</v>
+      </c>
+      <c r="O29" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
